--- a/services/service_alliance_trade.xlsx
+++ b/services/service_alliance_trade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\demo\capaStudy\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{894E0E63-E0BF-4268-B9B7-6787DD4CF070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF2D913-5A84-4966-B38C-D2BE563381D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F366FF44-2524-467D-ACB5-AA6E4A1C38B2}"/>
+    <workbookView xWindow="5130" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{F366FF44-2524-467D-ACB5-AA6E4A1C38B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="39">
   <si>
     <t>service</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -158,6 +158,10 @@
   </si>
   <si>
     <t>AE5</t>
+  </si>
+  <si>
+    <t>AE19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -549,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B274B0C-7C46-4E4A-8373-73036B9FE7FA}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
@@ -851,18 +855,18 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>31</v>
@@ -873,7 +877,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
@@ -884,12 +888,23 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/services/service_alliance_trade.xlsx
+++ b/services/service_alliance_trade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\demo\capaStudy\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF2D913-5A84-4966-B38C-D2BE563381D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855D23EA-CBE0-4DD1-8EEF-BC22758086AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{F366FF44-2524-467D-ACB5-AA6E4A1C38B2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F366FF44-2524-467D-ACB5-AA6E4A1C38B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="40">
   <si>
     <t>service</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -161,6 +161,10 @@
   </si>
   <si>
     <t>AE19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHOENIX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -553,8 +557,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B274B0C-7C46-4E4A-8373-73036B9FE7FA}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.46484375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
@@ -822,10 +829,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -833,7 +840,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>31</v>
@@ -844,7 +851,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>31</v>
@@ -855,7 +862,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>31</v>
@@ -866,18 +873,18 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
@@ -888,7 +895,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>31</v>
@@ -899,12 +906,23 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/services/service_alliance_trade.xlsx
+++ b/services/service_alliance_trade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\demo\capaStudy\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855D23EA-CBE0-4DD1-8EEF-BC22758086AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847175C3-7893-468C-8198-9D5E4B268DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F366FF44-2524-467D-ACB5-AA6E4A1C38B2}"/>
   </bookViews>
@@ -758,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
